--- a/testdata/testdata.xlsx
+++ b/testdata/testdata.xlsx
@@ -37,7 +37,7 @@
     <t>Summer</t>
   </si>
   <si>
-    <t>iPhone</t>
+    <t>Apple</t>
   </si>
   <si>
     <t>Red</t>
@@ -442,7 +442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -472,7 +472,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
